--- a/to-rust-as-we-fall/data/abilities/en/abilities.xlsx
+++ b/to-rust-as-we-fall/data/abilities/en/abilities.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abilities" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bindings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,17 +452,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>channels_hide_window.aster_focus</t>
+          <t>default.aster_focus</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TRACE</t>
+          <t>FOCUS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -471,83 +472,83 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aster pings the uneven surge rhythm.</t>
+          <t>Aster sharpens the lane read.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TRACE surfaces one known safe lure offset and one dead offset for this lane.</t>
+          <t>Aster's read spikes for a second before settling back into the fragment.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>channels_hide_window.peris_tune</t>
+          <t>default.endo_patch</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BLOOM</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Peris thickens the hush moss for a breath.</t>
+          <t>Endo patches the party back together.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BLOOM steadies the concealment patch if the pack is already sweeping the corridor mouth.</t>
+          <t>Endo buys the fragment a little more survivability.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>channels_hide_window.endo_patch</t>
+          <t>default.peris_tune</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BRACE</t>
+          <t>TUNE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Endo commits the fallback sprint.</t>
+          <t>Peris re-tunes the team's footing.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BRACE is a timing reminder: if the wash misses, go left into the corridor immediately.</t>
+          <t>Peris smooths the pressure in the room and gives the active lane back some stamina.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>channels_rhythm.aster_focus</t>
+          <t>channels_hide_window.aster_focus</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aster tags the surge rhythm.</t>
+          <t>Aster pings the uneven surge rhythm.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TRACE is flavor here: the lane logic itself already exposes the guarantee analysis.</t>
+          <t>TRACE surfaces one known safe lure offset and one dead offset for this lane.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>channels_rhythm.peris_tune</t>
+          <t>channels_hide_window.endo_patch</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BLOOM</t>
+          <t>BRACE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -594,29 +595,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Peris reads the corpse-side flora blur.</t>
+          <t>Endo commits the fallback sprint.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BLOOM highlights the corpse-side memory read and the lure spur, but it does not change the timing proof.</t>
+          <t>BRACE is a timing reminder: if the wash misses, go left into the corridor immediately.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>channels_rhythm.endo_patch</t>
+          <t>channels_hide_window.peris_tune</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BRACE</t>
+          <t>BLOOM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -626,24 +627,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Endo marks the fallback route.</t>
+          <t>Peris thickens the hush moss for a breath.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BRACE calls out the safe bridge arc after the washout resolves.</t>
+          <t>BLOOM steadies the concealment patch if the pack is already sweeping the corridor mouth.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>endo_junction_stretch.aster_focus</t>
+          <t>channels_rhythm.aster_focus</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -653,7 +654,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -663,56 +664,56 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aster aligns Endo's marks to the old facility grid.</t>
+          <t>Aster tags the surge rhythm.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TRACE can mark the safe ledge once Endo has shown the wall language.</t>
+          <t>TRACE is flavor here: the lane logic itself already exposes the guarantee analysis.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>endo_junction_stretch.peris_tune</t>
+          <t>channels_rhythm.endo_patch</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BLOOM</t>
+          <t>BRACE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Peris calms the dormant shelter flora.</t>
+          <t>Endo marks the fallback route.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BLOOM gives the party a little stamina margin before the last shelter push.</t>
+          <t>BRACE calls out the safe bridge arc after the washout resolves.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>endo_junction_stretch.endo_patch</t>
+          <t>channels_rhythm.peris_tune</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GUIDE</t>
+          <t>BLOOM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -722,194 +723,178 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Endo points out the route he trusts.</t>
+          <t>Peris reads the corpse-side flora blur.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GUIDE steadies Endo and highlights the practical survival anchors.</t>
+          <t>BLOOM highlights the corpse-side memory read and the lure spur, but it does not change the timing proof.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lockout_fragment.aster_focus</t>
+          <t>elevator.emp</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BURST</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Aster forces a burst window.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Burst buys Aster back a little stamina so the chase lane can be rehearsed repeatedly.</t>
-        </is>
-      </c>
+          <t>EMP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>lockout_fragment.peris_tune</t>
+          <t>endo_junction_stretch.aster_focus</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LURE</t>
+          <t>TRACE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Peris throws the sweep off-beat.</t>
+          <t>Aster aligns Endo's marks to the old facility grid.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Peris creates just enough noise to make the boundary feel briefly misaligned.</t>
+          <t>TRACE can mark the safe ledge once Endo has shown the wall language.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>lockout_fragment.endo_patch</t>
+          <t>endo_junction_stretch.endo_patch</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BRACE</t>
+          <t>GUIDE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Endo braces the team for impact.</t>
+          <t>Endo points out the route he trusts.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brace is a recovery tool for resetting the chase state without leaving the fragment.</t>
+          <t>GUIDE steadies Endo and highlights the practical survival anchors.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mother_ferrolure.aster_focus</t>
+          <t>endo_junction_stretch.peris_tune</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TRACE</t>
+          <t>BLOOM</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aster spikes the old portal routing tables.</t>
+          <t>Peris calms the dormant shelter flora.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TRACE buys an active bank a few more seconds of stability.</t>
+          <t>BLOOM gives the party a little stamina margin before the last shelter push.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mother_ferrolure.peris_tune</t>
+          <t>lockout_fragment.aster_focus</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BLOOM</t>
+          <t>BURST</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Peris reads the board through the mother's dormant buds.</t>
+          <t>Aster forces a burst window.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BLOOM sharpens the root and caretaker read in her overlay.</t>
+          <t>Burst buys Aster back a little stamina so the chase lane can be rehearsed repeatedly.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mother_ferrolure.endo_patch</t>
+          <t>lockout_fragment.endo_patch</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLOAK</t>
+          <t>BRACE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -919,125 +904,125 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Endo folds down into the chamber's blind spots.</t>
+          <t>Endo braces the team for impact.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CLOAK lets Endo ignore Techo lane damage for a few seconds while carrying the gear.</t>
+          <t>Brace is a recovery tool for resetting the chase state without leaving the fragment.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>overlay_lab.aster_focus</t>
+          <t>lockout_fragment.peris_tune</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TRACE</t>
+          <t>LURE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aster spikes the data lattice.</t>
+          <t>Peris throws the sweep off-beat.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Terminal links, portal IDs, and cached floor ghosts all brighten for a moment.</t>
+          <t>Peris creates just enough noise to make the boundary feel briefly misaligned.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>overlay_lab.peris_tune</t>
+          <t>mother_ferrolure.aster_focus</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BLOOM</t>
+          <t>TRACE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Peris wakes the nearby flora network.</t>
+          <t>Aster spikes the old portal routing tables.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Enemy blurs and client-memory traces ripple outward from the plants she already knows.</t>
+          <t>TRACE buys an active bank a few more seconds of stability.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>overlay_lab.endo_patch</t>
+          <t>mother_ferrolure.endo_patch</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SCROUNGE</t>
+          <t>CLOAK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Endo sweeps the room for survival anchors.</t>
+          <t>Endo folds down into the chamber's blind spots.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Food caches, hiding slots, and the shelter route flare brighter in the survival pass.</t>
+          <t>CLOAK lets Endo ignore Techo lane damage for a few seconds while carrying the gear.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>refuge_run.peris_tune</t>
+          <t>mother_ferrolure.peris_tune</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TEND</t>
+          <t>BLOOM</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1047,24 +1032,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Peris tends the hushbloom.</t>
+          <t>Peris reads the board through the mother's dormant buds.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TEND the hushbloom for a small stamina buffer before the run.</t>
+          <t>BLOOM sharpens the root and caretaker read in her overlay.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rings_fragment.aster_focus</t>
+          <t>overlay_lab.aster_focus</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>TRACE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1079,61 +1064,61 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aster reads the floral trace.</t>
+          <t>Aster spikes the data lattice.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aster treats the flora like evidence, mapping habit and memory into something legible.</t>
+          <t>Terminal links, portal IDs, and cached floor ghosts all brighten for a moment.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rings_fragment.peris_tune</t>
+          <t>overlay_lab.endo_patch</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TEND</t>
+          <t>SCROUNGE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Peris tends the bloom.</t>
+          <t>Endo sweeps the room for survival anchors.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Peris coaxes the fragment back toward intimacy instead of surveillance.</t>
+          <t>Food caches, hiding slots, and the shelter route flare brighter in the survival pass.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>rings_fragment.endo_patch</t>
+          <t>overlay_lab.peris_tune</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GRAFT</t>
+          <t>BLOOM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1143,61 +1128,45 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Endo grafts a steadier footing into the lane.</t>
+          <t>Peris wakes the nearby flora network.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Endo keeps the party stable enough to linger in the alcoves instead of bouncing out of them.</t>
+          <t>Enemy blurs and client-memory traces ripple outward from the plants she already knows.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>stacks_fragment.aster_focus</t>
+          <t>peris_sim.protect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SCAN</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Aster scans the tuned lane.</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Aster peels back the polished surface and catches the hand-tuned signal work underneath it.</t>
-        </is>
-      </c>
+          <t>PROTECT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>stacks_fragment.peris_tune</t>
+          <t>refuge_run.peris_tune</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SYNC</t>
+          <t>TEND</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1207,56 +1176,56 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Peris syncs the team's pace.</t>
+          <t>Peris tends the hushbloom.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Peris settles the room enough for the lane to feel collaborative instead of clinical.</t>
+          <t>TEND the hushbloom for a small stamina buffer before the run.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>stacks_fragment.endo_patch</t>
+          <t>rings_fragment.aster_focus</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CACHE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Endo caches the current read.</t>
+          <t>Aster reads the floral trace.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Endo banks a little safety so you can stay in the lane and keep exploring the station beats.</t>
+          <t>Aster treats the flora like evidence, mapping habit and memory into something legible.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>survival_range.aster_focus</t>
+          <t>rings_fragment.endo_patch</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MARK</t>
+          <t>GRAFT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1266,34 +1235,34 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aster tightens the route read.</t>
+          <t>Endo grafts a steadier footing into the lane.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MARK sharpens the scout read and can stand in for a last-second lane check at the perch.</t>
+          <t>Endo keeps the party stable enough to linger in the alcoves instead of bouncing out of them.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>survival_range.peris_tune</t>
+          <t>rings_fragment.peris_tune</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BLOOM</t>
+          <t>TEND</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1303,78 +1272,424 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Peris retunes the lure pulse.</t>
+          <t>Peris tends the bloom.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BLOOM stretches the lure window if the team hesitates on the way into the slit.</t>
+          <t>Peris coaxes the fragment back toward intimacy instead of surveillance.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>survival_range.endo_patch</t>
+          <t>stacks_fragment.aster_focus</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BRACE</t>
+          <t>SCAN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Endo steadies the run.</t>
+          <t>Aster scans the tuned lane.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BRACE buys back some margin before the shelter sprint.</t>
+          <t>Aster peels back the polished surface and catches the hand-tuned signal work underneath it.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>peris_sim.protect</t>
+          <t>stacks_fragment.endo_patch</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PROTECT</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+          <t>CACHE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Endo caches the current read.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Endo banks a little safety so you can stay in the lane and keep exploring the station beats.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>elevator.emp</t>
+          <t>stacks_fragment.peris_tune</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EMP</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+          <t>SYNC</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Peris syncs the team's pace.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Peris settles the room enough for the lane to feel collaborative instead of clinical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>survival_range.aster_focus</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MARK</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aster tightens the route read.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>MARK sharpens the scout read and can stand in for a last-second lane check at the perch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>survival_range.endo_patch</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BRACE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Endo steadies the run.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>BRACE buys back some margin before the shelter sprint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>survival_range.peris_tune</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BLOOM</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Peris retunes the lure pulse.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>BLOOM stretches the lure window if the team hesitates on the way into the slit.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>keybind</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>atp_cost</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>active_status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>sta_delta</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>hp_delta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aster_focus</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>aster</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.29,0.62,1.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>attacking</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>peris_tune</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>peris</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.0,0.67,0.27</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>attacking</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>endo_patch</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>endo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.4,0.72,0.55</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>resting</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>protect</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>peris</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.8,0.55,0.2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>emp</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>aster</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.29,0.62,1.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/to-rust-as-we-fall/data/abilities/en/abilities.xlsx
+++ b/to-rust-as-we-fall/data/abilities/en/abilities.xlsx
@@ -748,10 +748,6 @@
           <t>EMP</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1148,10 +1144,6 @@
           <t>PROTECT</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1560,8 +1552,6 @@
           <t>attacking</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1599,7 +1589,6 @@
           <t>18.0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1632,7 +1621,6 @@
           <t>resting</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>12.0</t>
@@ -1660,10 +1648,6 @@
           <t>0.8,0.55,0.2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1678,7 +1662,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1686,10 +1670,6 @@
           <t>0.29,0.62,1.0</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/to-rust-as-we-fall/data/abilities/en/abilities.xlsx
+++ b/to-rust-as-we-fall/data/abilities/en/abilities.xlsx
@@ -944,7 +944,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mother_ferrolure.aster_focus</t>
+          <t>mother_flure.aster_focus</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -976,7 +976,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mother_ferrolure.endo_patch</t>
+          <t>mother_flure.endo_patch</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1008,7 +1008,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mother_ferrolure.peris_tune</t>
+          <t>mother_flure.peris_tune</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">

--- a/to-rust-as-we-fall/data/abilities/en/abilities.xlsx
+++ b/to-rust-as-we-fall/data/abilities/en/abilities.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1462,6 +1462,38 @@
       <c r="F34" t="inlineStr">
         <is>
           <t>BLOOM stretches the lure window if the team hesitates on the way into the slit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>data_fragment.peris_harvest</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HARVEST</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Just pretty. Nothing to take.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ornamental growth reads yellow. Once read, it can be cleared.</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1671,6 +1703,28 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>peris_harvest</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>peris</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1.0,0.84,0.25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
